--- a/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9586" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9585" uniqueCount="645">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8902,7 +8902,7 @@
         <v>112</v>
       </c>
       <c r="F65" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>76</v>
@@ -9125,9 +9125,7 @@
       <c r="K67" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="L67" t="s" s="2">
-        <v>257</v>
-      </c>
+      <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
         <v>123</v>
       </c>
@@ -12986,7 +12984,7 @@
         <v>112</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G105" t="s" s="2">
         <v>76</v>
@@ -16452,7 +16450,7 @@
         <v>112</v>
       </c>
       <c r="F139" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>76</v>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-examens-de-biologie-medicale.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
